--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-23T20:16:24.545Z</t>
+    <t>2026-09-23T22:02:58.118Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,13 +52,52 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-23T22:02:58.118Z</t>
+    <t>2026-09-24T14:37:24.851Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>
   </si>
   <si>
     <t>https://www.compliancesigns.com/</t>
+  </si>
+  <si>
+    <t>c/chemical-hazard-safety-signs.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>c/chemical-hazard-safety-signs</t>
+  </si>
+  <si>
+    <t>2026-09-24T14:34:58.898Z</t>
+  </si>
+  <si>
+    <t>https://www.compliancesigns.com/c/chemical-hazard-safety-signs</t>
+  </si>
+  <si>
+    <t>pd/oneok-spottters-rerquired-sign-cs949629.report.json</t>
+  </si>
+  <si>
+    <t>pd/oneok-spottters-rerquired-sign-cs949629</t>
+  </si>
+  <si>
+    <t>2026-09-24T14:33:04.786Z</t>
+  </si>
+  <si>
+    <t>https://www.compliancesigns.com/pd/oneok-spottters-rerquired-sign-cs949629</t>
+  </si>
+  <si>
+    <t>products/safety-labels.report.json</t>
+  </si>
+  <si>
+    <t>products/safety-labels</t>
+  </si>
+  <si>
+    <t>2026-09-24T14:34:03.397Z</t>
+  </si>
+  <si>
+    <t>https://www.compliancesigns.com/products/safety-labels</t>
   </si>
 </sst>
 </file>
@@ -447,16 +486,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -509,6 +546,84 @@
       </c>
       <c r="H2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T14:37:24.851Z</t>
+    <t>2026-09-24T14:47:21.561Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["cards-promo","cards-category","cards-product","tabs-industry","cards-review","cards-blog","cards-value"]</t>
+    <t>["cards-promo","cards-category","cards-product","tabs-industry","cards-review","cards-blog","cards-value","newsletter"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T14:47:21.561Z</t>
+    <t>2026-09-24T15:17:30.773Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T15:17:30.773Z</t>
+    <t>2026-09-24T16:14:52.739Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T16:14:52.739Z</t>
+    <t>2026-09-24T16:21:16.195Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T16:21:16.195Z</t>
+    <t>2026-09-24T16:31:53.084Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T16:31:53.084Z</t>
+    <t>2026-09-24T16:37:21.059Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T16:37:21.059Z</t>
+    <t>2026-09-24T16:53:31.195Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T16:53:31.195Z</t>
+    <t>2026-09-24T17:37:02.944Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>

--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-09-24T17:37:02.944Z</t>
+    <t>2026-09-25T20:36:14.951Z</t>
   </si>
   <si>
     <t>Safety Signs, Tags, Labels - Guaranteed Compliance</t>
